--- a/data/测试集_40段_第一轮.xlsx
+++ b/data/测试集_40段_第一轮.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7695" tabRatio="500"/>
+    <workbookView windowWidth="20490" windowHeight="7095" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="测试集" sheetId="1" r:id="rId1"/>
@@ -1982,16 +1982,66 @@
     <t>R4-04</t>
   </si>
   <si>
-    <t>顾客：手机收到不满意，申请退款。
-客服：亲，这单金额比较大，为了保障您的资金安全，需要您上传一下身份证正反面照片核实身份哦～
-顾客：之前退款没要求过啊。
-客服：大额订单都会核实的呢～</t>
+    <r>
+      <t>顾客：我买的奶粉想退货，怎么退？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：好的，请把您孩子的姓名、出生日期、过敏史发给我，我们需要记录在案。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：退货为什么要这些？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：这是我们的售后流程，需要建立客户档案</t>
+    </r>
   </si>
   <si>
     <t>《实施条例》第二十三条第一款；《保护法》第二十九条第一款</t>
   </si>
   <si>
-    <t>退款原路返回，用不到证件照（此题标准答案由本人判定）</t>
+    <t>退货不需要儿童姓名、出生日期、过敏史，且儿童健康信息属于敏感个人信息，索要明显与售后无直接关系</t>
   </si>
   <si>
     <t>R5-01</t>
@@ -6080,7 +6130,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" ht="61.5" customHeight="1" spans="1:14">
+    <row r="2" ht="61.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A2" s="11" t="s">
         <v>14</v>
       </c>
@@ -6119,7 +6169,7 @@
       <c r="M2" s="15"/>
       <c r="N2" s="15"/>
     </row>
-    <row r="3" ht="75.75" customHeight="1" spans="1:14">
+    <row r="3" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A3" s="11" t="s">
         <v>22</v>
       </c>
@@ -6158,7 +6208,7 @@
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
     </row>
-    <row r="4" ht="75.75" customHeight="1" spans="1:14">
+    <row r="4" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A4" s="11" t="s">
         <v>26</v>
       </c>
@@ -6197,7 +6247,7 @@
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
     </row>
-    <row r="5" ht="75.75" customHeight="1" spans="1:14">
+    <row r="5" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A5" s="11" t="s">
         <v>30</v>
       </c>
@@ -6236,7 +6286,7 @@
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
     </row>
-    <row r="6" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="6" ht="75.75" customHeight="1" spans="1:14">
       <c r="A6" s="11" t="s">
         <v>34</v>
       </c>
@@ -6271,7 +6321,7 @@
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
     </row>
-    <row r="7" ht="61.5" customHeight="1" spans="1:14">
+    <row r="7" ht="61.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A7" s="11" t="s">
         <v>39</v>
       </c>
@@ -6310,7 +6360,7 @@
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
     </row>
-    <row r="8" ht="75.75" customHeight="1" spans="1:14">
+    <row r="8" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A8" s="11" t="s">
         <v>44</v>
       </c>
@@ -6349,7 +6399,7 @@
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
     </row>
-    <row r="9" ht="90" customHeight="1" spans="1:14">
+    <row r="9" ht="90" hidden="1" customHeight="1" spans="1:14">
       <c r="A9" s="11" t="s">
         <v>48</v>
       </c>
@@ -6388,7 +6438,7 @@
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
     </row>
-    <row r="10" ht="61.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="10" ht="61.5" customHeight="1" spans="1:14">
       <c r="A10" s="11" t="s">
         <v>52</v>
       </c>
@@ -6423,7 +6473,7 @@
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
     </row>
-    <row r="11" ht="90" customHeight="1" spans="1:14">
+    <row r="11" ht="90" hidden="1" customHeight="1" spans="1:14">
       <c r="A11" s="11" t="s">
         <v>55</v>
       </c>
@@ -6462,7 +6512,7 @@
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
     </row>
-    <row r="12" ht="145.5" customHeight="1" spans="1:14">
+    <row r="12" ht="145.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A12" s="11" t="s">
         <v>61</v>
       </c>
@@ -6501,7 +6551,7 @@
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
     </row>
-    <row r="13" ht="103.5" customHeight="1" spans="1:14">
+    <row r="13" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A13" s="11" t="s">
         <v>65</v>
       </c>
@@ -6540,7 +6590,7 @@
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
     </row>
-    <row r="14" ht="103.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="14" ht="103.5" customHeight="1" spans="1:14">
       <c r="A14" s="11" t="s">
         <v>69</v>
       </c>
@@ -6575,7 +6625,7 @@
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
     </row>
-    <row r="15" ht="75.75" customHeight="1" spans="1:14">
+    <row r="15" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A15" s="11" t="s">
         <v>73</v>
       </c>
@@ -6614,7 +6664,7 @@
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
     </row>
-    <row r="16" ht="103.5" customHeight="1" spans="1:14">
+    <row r="16" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A16" s="11" t="s">
         <v>78</v>
       </c>
@@ -6653,7 +6703,7 @@
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
     </row>
-    <row r="17" ht="103.5" customHeight="1" spans="1:14">
+    <row r="17" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A17" s="11" t="s">
         <v>82</v>
       </c>
@@ -6692,14 +6742,14 @@
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
     </row>
-    <row r="18" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="18" ht="75.75" customHeight="1" spans="1:14">
       <c r="A18" s="11" t="s">
         <v>87</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="16" t="s">
         <v>88</v>
       </c>
       <c r="D18" s="12" t="s">
@@ -6715,7 +6765,7 @@
         <v>59</v>
       </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="13" t="s">
+      <c r="I18" s="16" t="s">
         <v>90</v>
       </c>
       <c r="J18" s="15"/>
@@ -6727,7 +6777,7 @@
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
     </row>
-    <row r="19" ht="75.75" customHeight="1" spans="1:14">
+    <row r="19" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A19" s="11" t="s">
         <v>91</v>
       </c>
@@ -6766,7 +6816,7 @@
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
     </row>
-    <row r="20" ht="90" customHeight="1" spans="1:14">
+    <row r="20" ht="90" hidden="1" customHeight="1" spans="1:14">
       <c r="A20" s="11" t="s">
         <v>96</v>
       </c>
@@ -6805,7 +6855,7 @@
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
     </row>
-    <row r="21" ht="61.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="21" ht="61.5" customHeight="1" spans="1:14">
       <c r="A21" s="11" t="s">
         <v>99</v>
       </c>
@@ -6840,7 +6890,7 @@
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
     </row>
-    <row r="22" ht="75.75" customHeight="1" spans="1:14">
+    <row r="22" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A22" s="12" t="s">
         <v>102</v>
       </c>
@@ -6879,7 +6929,7 @@
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
     </row>
-    <row r="23" ht="61.5" customHeight="1" spans="1:14">
+    <row r="23" ht="61.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A23" s="12" t="s">
         <v>107</v>
       </c>
@@ -6918,7 +6968,7 @@
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
     </row>
-    <row r="24" ht="61.5" customHeight="1" spans="1:14">
+    <row r="24" ht="61.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A24" s="12" t="s">
         <v>110</v>
       </c>
@@ -6957,7 +7007,7 @@
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
     </row>
-    <row r="25" ht="90" hidden="1" customHeight="1" spans="1:14">
+    <row r="25" ht="90" customHeight="1" spans="1:14">
       <c r="A25" s="12" t="s">
         <v>114</v>
       </c>
@@ -6992,7 +7042,7 @@
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
     </row>
-    <row r="26" ht="61.5" customHeight="1" spans="1:14">
+    <row r="26" ht="61.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A26" s="12" t="s">
         <v>118</v>
       </c>
@@ -7031,7 +7081,7 @@
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
     </row>
-    <row r="27" ht="61.5" customHeight="1" spans="1:14">
+    <row r="27" ht="61.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A27" s="12" t="s">
         <v>122</v>
       </c>
@@ -7070,7 +7120,7 @@
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
     </row>
-    <row r="28" ht="75.75" customHeight="1" spans="1:14">
+    <row r="28" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A28" s="12" t="s">
         <v>126</v>
       </c>
@@ -7111,7 +7161,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" ht="117.75" customHeight="1" spans="1:14">
+    <row r="29" ht="117.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A29" s="12" t="s">
         <v>133</v>
       </c>
@@ -7148,7 +7198,7 @@
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
     </row>
-    <row r="30" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="30" ht="75.75" customHeight="1" spans="1:14">
       <c r="A30" s="12" t="s">
         <v>138</v>
       </c>
@@ -7183,7 +7233,7 @@
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
     </row>
-    <row r="31" ht="75.75" customHeight="1" spans="1:14">
+    <row r="31" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A31" s="12" t="s">
         <v>142</v>
       </c>
@@ -7220,7 +7270,7 @@
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
     </row>
-    <row r="32" ht="90" customHeight="1" spans="1:14">
+    <row r="32" ht="90" hidden="1" customHeight="1" spans="1:14">
       <c r="A32" s="12" t="s">
         <v>146</v>
       </c>
@@ -7257,7 +7307,7 @@
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
     </row>
-    <row r="33" ht="61.5" customHeight="1" spans="1:14">
+    <row r="33" ht="61.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A33" s="12" t="s">
         <v>149</v>
       </c>
@@ -7294,7 +7344,7 @@
       <c r="M33" s="15"/>
       <c r="N33" s="15"/>
     </row>
-    <row r="34" ht="75.75" customHeight="1" spans="1:14">
+    <row r="34" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A34" s="12" t="s">
         <v>153</v>
       </c>
@@ -7331,7 +7381,7 @@
       <c r="M34" s="15"/>
       <c r="N34" s="15"/>
     </row>
-    <row r="35" ht="117.75" customHeight="1" spans="1:14">
+    <row r="35" ht="117.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A35" s="12" t="s">
         <v>157</v>
       </c>
@@ -7368,7 +7418,7 @@
       <c r="M35" s="15"/>
       <c r="N35" s="15"/>
     </row>
-    <row r="36" ht="103.5" customHeight="1" spans="1:14">
+    <row r="36" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A36" s="12" t="s">
         <v>161</v>
       </c>
@@ -7405,7 +7455,7 @@
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
     </row>
-    <row r="37" ht="103.5" customHeight="1" spans="1:14">
+    <row r="37" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A37" s="12" t="s">
         <v>165</v>
       </c>
@@ -7442,7 +7492,7 @@
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
     </row>
-    <row r="38" ht="103.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="38" ht="103.5" customHeight="1" spans="1:14">
       <c r="A38" s="12" t="s">
         <v>170</v>
       </c>
@@ -7477,7 +7527,7 @@
       <c r="M38" s="15"/>
       <c r="N38" s="15"/>
     </row>
-    <row r="39" ht="103.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="39" ht="103.5" customHeight="1" spans="1:14">
       <c r="A39" s="12" t="s">
         <v>173</v>
       </c>
@@ -7512,7 +7562,7 @@
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
     </row>
-    <row r="40" ht="103.5" customHeight="1" spans="1:14">
+    <row r="40" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A40" s="12" t="s">
         <v>176</v>
       </c>
@@ -7549,7 +7599,7 @@
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
     </row>
-    <row r="41" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="41" ht="75.75" customHeight="1" spans="1:14">
       <c r="A41" s="12" t="s">
         <v>179</v>
       </c>
@@ -7587,9 +7637,9 @@
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N41" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="equal" val="前30"/>
-      </customFilters>
+      <filters>
+        <filter val="后10"/>
+      </filters>
     </filterColumn>
     <extLst/>
   </autoFilter>

--- a/data/测试集_40段_第一轮.xlsx
+++ b/data/测试集_40段_第一轮.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Desktop\项目一\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="198">
   <si>
     <t>编号</t>
   </si>
@@ -1983,6 +1983,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>顾客：我买的奶粉想退货，怎么退？</t>
     </r>
     <r>
@@ -2656,171 +2661,80 @@
         <rFont val="Noto Sans CJK SC"/>
         <charset val="134"/>
       </rPr>
-      <t>待</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>R4-01</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：吃了你们的零食肚子疼，你们得给个说法。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：非常抱歉。麻烦您提供一下就诊记录，我们好评估赔偿。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：需要这个吗？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：赔偿金额要依据就诊费用核算的。</t>
-    </r>
-  </si>
-  <si>
-    <t>《实施条例》第二十三条第二款</t>
-  </si>
-  <si>
-    <t>缺的信息：消费者是否主张医疗费用赔偿，无法判断收集是否必要</t>
+      <t>合规</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <charset val="1"/>
+      </rPr>
+      <t>-01</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：面霜收到四天，想退货。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：亲，请问包装和封口膜是否完好呢？</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>顾客：封口膜我撕开了，已经用了差不多四分之一瓶，觉得不适合我。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服：亲，化妆品的封口膜属于必要的一次性密封包装，已经撕开并且用了不少，影响二次销售，这种情况不支持无理由退货哦～如果是质量问题，您可以拍照给我，我们再帮您处理。</t>
+    </r>
   </si>
   <si>
     <t>合规</t>
-  </si>
-  <si>
-    <t>规则没写清，待复核题的触发条件不够明确。</t>
-  </si>
-  <si>
-    <t>此题有争议，顾客表述不明确，判合规亦言之有理。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t>合规</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>-01</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：面霜收到四天，想退货。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：亲，请问包装和封口膜是否完好呢？</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>顾客：封口膜我撕开了，已经用了差不多四分之一瓶，觉得不适合我。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>客服：亲，化妆品的封口膜属于必要的一次性密封包装，已经撕开并且用了不少，影响二次销售，这种情况不支持无理由退货哦～如果是质量问题，您可以拍照给我，我们再帮您处理。</t>
-    </r>
   </si>
   <si>
     <t>《暂行办法》第九条第（一）项</t>
@@ -4126,6 +4040,101 @@
         <charset val="134"/>
       </rPr>
       <t>是一对反例：同样报出地址，一个报错了人，一个报对了人</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>合规</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>-14</t>
+    </r>
+  </si>
+  <si>
+    <t>顾客：我买的蓝牙耳机三个月前坏了，当时你们帮我维修好了，现在又坏了同样的地方，还能修吗？
+客服：您好，您的耳机我们记录显示是三个月前维修过，维修后的保修期是三个月，今天刚好到期。按照规定，保修期内免费维修，今天的话需要收取维修费用。
+顾客：刚好到期就要收费？
+客服：是的，保修期自维修完成之日起计算，今天确实是最后一天，已经到期了。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无需引用条文（用于测试是否误报</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>R3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>客服收费是有依据的（维修保修期到期），不是无理拒绝，但对话里有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>需要收取维修费用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>容易被误判成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <charset val="134"/>
+      </rPr>
+      <t>R3</t>
     </r>
   </si>
   <si>
@@ -5496,7 +5505,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5545,6 +5554,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -6130,7 +6142,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" ht="61.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="2" ht="61.5" customHeight="1" spans="1:14">
       <c r="A2" s="11" t="s">
         <v>14</v>
       </c>
@@ -6169,7 +6181,7 @@
       <c r="M2" s="15"/>
       <c r="N2" s="15"/>
     </row>
-    <row r="3" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="3" ht="75.75" customHeight="1" spans="1:14">
       <c r="A3" s="11" t="s">
         <v>22</v>
       </c>
@@ -6208,7 +6220,7 @@
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
     </row>
-    <row r="4" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="4" ht="75.75" customHeight="1" spans="1:14">
       <c r="A4" s="11" t="s">
         <v>26</v>
       </c>
@@ -6247,7 +6259,7 @@
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
     </row>
-    <row r="5" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="5" ht="75.75" customHeight="1" spans="1:14">
       <c r="A5" s="11" t="s">
         <v>30</v>
       </c>
@@ -6286,7 +6298,7 @@
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
     </row>
-    <row r="6" ht="75.75" customHeight="1" spans="1:14">
+    <row r="6" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A6" s="11" t="s">
         <v>34</v>
       </c>
@@ -6321,7 +6333,7 @@
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
     </row>
-    <row r="7" ht="61.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="7" ht="61.5" customHeight="1" spans="1:14">
       <c r="A7" s="11" t="s">
         <v>39</v>
       </c>
@@ -6360,7 +6372,7 @@
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
     </row>
-    <row r="8" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="8" ht="75.75" customHeight="1" spans="1:14">
       <c r="A8" s="11" t="s">
         <v>44</v>
       </c>
@@ -6399,7 +6411,7 @@
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
     </row>
-    <row r="9" ht="90" hidden="1" customHeight="1" spans="1:14">
+    <row r="9" ht="90" customHeight="1" spans="1:14">
       <c r="A9" s="11" t="s">
         <v>48</v>
       </c>
@@ -6438,7 +6450,7 @@
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
     </row>
-    <row r="10" ht="61.5" customHeight="1" spans="1:14">
+    <row r="10" ht="61.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A10" s="11" t="s">
         <v>52</v>
       </c>
@@ -6473,7 +6485,7 @@
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
     </row>
-    <row r="11" ht="90" hidden="1" customHeight="1" spans="1:14">
+    <row r="11" ht="90" customHeight="1" spans="1:14">
       <c r="A11" s="11" t="s">
         <v>55</v>
       </c>
@@ -6512,7 +6524,7 @@
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
     </row>
-    <row r="12" ht="145.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="12" ht="145.5" customHeight="1" spans="1:14">
       <c r="A12" s="11" t="s">
         <v>61</v>
       </c>
@@ -6551,7 +6563,7 @@
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
     </row>
-    <row r="13" ht="103.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="13" ht="103.5" customHeight="1" spans="1:14">
       <c r="A13" s="11" t="s">
         <v>65</v>
       </c>
@@ -6590,7 +6602,7 @@
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
     </row>
-    <row r="14" ht="103.5" customHeight="1" spans="1:14">
+    <row r="14" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A14" s="11" t="s">
         <v>69</v>
       </c>
@@ -6625,7 +6637,7 @@
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
     </row>
-    <row r="15" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="15" ht="75.75" customHeight="1" spans="1:14">
       <c r="A15" s="11" t="s">
         <v>73</v>
       </c>
@@ -6664,7 +6676,7 @@
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
     </row>
-    <row r="16" ht="103.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="16" ht="103.5" customHeight="1" spans="1:14">
       <c r="A16" s="11" t="s">
         <v>78</v>
       </c>
@@ -6703,7 +6715,7 @@
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
     </row>
-    <row r="17" ht="103.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="17" ht="103.5" customHeight="1" spans="1:14">
       <c r="A17" s="11" t="s">
         <v>82</v>
       </c>
@@ -6742,7 +6754,7 @@
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
     </row>
-    <row r="18" ht="75.75" customHeight="1" spans="1:14">
+    <row r="18" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A18" s="11" t="s">
         <v>87</v>
       </c>
@@ -6777,7 +6789,7 @@
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
     </row>
-    <row r="19" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="19" ht="75.75" customHeight="1" spans="1:14">
       <c r="A19" s="11" t="s">
         <v>91</v>
       </c>
@@ -6816,7 +6828,7 @@
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
     </row>
-    <row r="20" ht="90" hidden="1" customHeight="1" spans="1:14">
+    <row r="20" ht="90" customHeight="1" spans="1:14">
       <c r="A20" s="11" t="s">
         <v>96</v>
       </c>
@@ -6855,7 +6867,7 @@
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
     </row>
-    <row r="21" ht="61.5" customHeight="1" spans="1:14">
+    <row r="21" ht="61.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A21" s="11" t="s">
         <v>99</v>
       </c>
@@ -6890,7 +6902,7 @@
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
     </row>
-    <row r="22" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="22" ht="75.75" customHeight="1" spans="1:14">
       <c r="A22" s="12" t="s">
         <v>102</v>
       </c>
@@ -6929,7 +6941,7 @@
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
     </row>
-    <row r="23" ht="61.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="23" ht="61.5" customHeight="1" spans="1:14">
       <c r="A23" s="12" t="s">
         <v>107</v>
       </c>
@@ -6968,7 +6980,7 @@
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
     </row>
-    <row r="24" ht="61.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="24" ht="61.5" customHeight="1" spans="1:14">
       <c r="A24" s="12" t="s">
         <v>110</v>
       </c>
@@ -7007,7 +7019,7 @@
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
     </row>
-    <row r="25" ht="90" customHeight="1" spans="1:14">
+    <row r="25" ht="90" hidden="1" customHeight="1" spans="1:14">
       <c r="A25" s="12" t="s">
         <v>114</v>
       </c>
@@ -7042,7 +7054,7 @@
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
     </row>
-    <row r="26" ht="61.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="26" ht="61.5" customHeight="1" spans="1:14">
       <c r="A26" s="12" t="s">
         <v>118</v>
       </c>
@@ -7081,7 +7093,7 @@
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
     </row>
-    <row r="27" ht="61.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="27" ht="61.5" customHeight="1" spans="1:14">
       <c r="A27" s="12" t="s">
         <v>122</v>
       </c>
@@ -7120,7 +7132,7 @@
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
     </row>
-    <row r="28" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="28" ht="117.75" customHeight="1" spans="1:14">
       <c r="A28" s="12" t="s">
         <v>126</v>
       </c>
@@ -7131,136 +7143,132 @@
         <v>127</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>75</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="E28" s="11"/>
       <c r="F28" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="J28" s="14" t="s">
         <v>128</v>
-      </c>
-      <c r="G28" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>130</v>
       </c>
       <c r="K28" s="15"/>
       <c r="L28" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>错</v>
-      </c>
-      <c r="M28" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="N28" s="14" t="s">
+        <v>对</v>
+      </c>
+      <c r="M28" s="15"/>
+      <c r="N28" s="15"/>
+    </row>
+    <row r="29" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+      <c r="A29" s="12" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="29" ht="117.75" hidden="1" customHeight="1" spans="1:14">
-      <c r="A29" s="12" t="s">
+      <c r="B29" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>134</v>
-      </c>
       <c r="D29" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E29" s="11"/>
       <c r="F29" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="G29" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="I29" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="G29" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H29" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="J29" s="14" t="s">
-        <v>130</v>
-      </c>
+      <c r="J29" s="15"/>
       <c r="K29" s="15"/>
       <c r="L29" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>对</v>
+        <v/>
       </c>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
     </row>
     <row r="30" ht="75.75" customHeight="1" spans="1:14">
       <c r="A30" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>139</v>
+        <v>15</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>137</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="J30" s="15"/>
+        <v>139</v>
+      </c>
+      <c r="J30" s="14" t="s">
+        <v>128</v>
+      </c>
       <c r="K30" s="15"/>
       <c r="L30" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>对</v>
       </c>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
     </row>
-    <row r="31" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="31" ht="90" customHeight="1" spans="1:14">
       <c r="A31" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="13" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J31" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K31" s="15"/>
       <c r="L31" s="11" t="str">
@@ -7270,34 +7278,34 @@
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
     </row>
-    <row r="32" ht="90" hidden="1" customHeight="1" spans="1:14">
+    <row r="32" ht="61.5" customHeight="1" spans="1:14">
       <c r="A32" s="12" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E32" s="11"/>
       <c r="F32" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="J32" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K32" s="15"/>
       <c r="L32" s="11" t="str">
@@ -7307,34 +7315,34 @@
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
     </row>
-    <row r="33" ht="61.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="33" ht="75.75" customHeight="1" spans="1:14">
       <c r="A33" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E33" s="11"/>
       <c r="F33" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="J33" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K33" s="15"/>
       <c r="L33" s="11" t="str">
@@ -7344,34 +7352,34 @@
       <c r="M33" s="15"/>
       <c r="N33" s="15"/>
     </row>
-    <row r="34" ht="75.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="34" ht="117.75" customHeight="1" spans="1:14">
       <c r="A34" s="12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E34" s="11"/>
       <c r="F34" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="J34" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K34" s="15"/>
       <c r="L34" s="11" t="str">
@@ -7381,34 +7389,34 @@
       <c r="M34" s="15"/>
       <c r="N34" s="15"/>
     </row>
-    <row r="35" ht="117.75" hidden="1" customHeight="1" spans="1:14">
+    <row r="35" ht="103.5" customHeight="1" spans="1:14">
       <c r="A35" s="12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E35" s="11"/>
       <c r="F35" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="H35" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J35" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K35" s="15"/>
       <c r="L35" s="11" t="str">
@@ -7418,34 +7426,34 @@
       <c r="M35" s="15"/>
       <c r="N35" s="15"/>
     </row>
-    <row r="36" ht="103.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="36" ht="103.5" customHeight="1" spans="1:14">
       <c r="A36" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G36" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="I36" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="G36" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H36" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>164</v>
-      </c>
       <c r="J36" s="14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K36" s="15"/>
       <c r="L36" s="11" t="str">
@@ -7457,66 +7465,64 @@
     </row>
     <row r="37" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A37" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>166</v>
-      </c>
       <c r="D37" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="13" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>130</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="J37" s="15"/>
       <c r="K37" s="15"/>
       <c r="L37" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>对</v>
+        <v/>
       </c>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
     </row>
-    <row r="38" ht="103.5" customHeight="1" spans="1:14">
+    <row r="38" ht="103.5" hidden="1" customHeight="1" spans="1:14">
       <c r="A38" s="12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E38" s="11"/>
       <c r="F38" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
@@ -7529,117 +7535,117 @@
     </row>
     <row r="39" ht="103.5" customHeight="1" spans="1:14">
       <c r="A39" s="12" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>174</v>
+        <v>15</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>171</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E39" s="11"/>
       <c r="F39" s="13" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="J39" s="15"/>
+        <v>172</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>128</v>
+      </c>
       <c r="K39" s="15"/>
       <c r="L39" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>对</v>
       </c>
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
     </row>
-    <row r="40" ht="103.5" hidden="1" customHeight="1" spans="1:14">
+    <row r="40" ht="75.75" hidden="1" customHeight="1" spans="1:14">
       <c r="A40" s="12" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="16" t="s">
-        <v>177</v>
+        <v>35</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>174</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E40" s="11"/>
       <c r="F40" s="13" t="s">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>130</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="J40" s="15"/>
       <c r="K40" s="15"/>
       <c r="L40" s="11" t="str">
         <f t="shared" si="0"/>
-        <v>对</v>
+        <v/>
       </c>
       <c r="M40" s="15"/>
       <c r="N40" s="15"/>
     </row>
     <row r="41" ht="75.75" customHeight="1" spans="1:14">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="D41" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="E41" s="11"/>
+      <c r="F41" s="16" t="s">
         <v>179</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="E41" s="11"/>
-      <c r="F41" s="13" t="s">
-        <v>181</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="H41" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="I41" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="J41" s="15"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>128</v>
+      </c>
       <c r="K41" s="15"/>
       <c r="L41" s="11" t="str">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="M41" s="15"/>
-      <c r="N41" s="15"/>
+        <v>对</v>
+      </c>
+      <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:N41" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="1">
-      <filters>
-        <filter val="后10"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="前30"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>
@@ -7672,7 +7678,7 @@
   <sheetData>
     <row r="1" customHeight="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7685,19 +7691,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -7705,11 +7711,11 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <f>COUNTIFS(测试集!$D$2:$D$41,A3,测试集!$B$2:$B$41,"前30")</f>
+        <f>COUNTIFS(测试集!$D$2:$D$40,A3,测试集!$B$2:$B$40,"前30")</f>
         <v>15</v>
       </c>
       <c r="C3" s="3">
-        <f>COUNTIFS(测试集!$D$2:$D$41,A3,测试集!$B$2:$B$41,"后10")</f>
+        <f>COUNTIFS(测试集!$D$2:$D$40,A3,测试集!$B$2:$B$40,"后10")</f>
         <v>5</v>
       </c>
       <c r="D3" s="3">
@@ -7729,35 +7735,35 @@
         <v>104</v>
       </c>
       <c r="B4" s="3">
-        <f>COUNTIFS(测试集!$D$2:$D$41,A4,测试集!$B$2:$B$41,"前30")</f>
-        <v>6</v>
+        <f>COUNTIFS(测试集!$D$2:$D$40,A4,测试集!$B$2:$B$40,"前30")</f>
+        <v>5</v>
       </c>
       <c r="C4" s="3">
-        <f>COUNTIFS(测试集!$D$2:$D$41,A4,测试集!$B$2:$B$41,"后10")</f>
+        <f>COUNTIFS(测试集!$D$2:$D$40,A4,测试集!$B$2:$B$40,"后10")</f>
         <v>1</v>
       </c>
       <c r="D4" s="3">
         <f>B4+C4</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4">
         <v>7</v>
       </c>
       <c r="F4" s="3" t="str">
         <f>IF(D4=E4,"一致","不一致")</f>
-        <v>一致</v>
+        <v>不一致</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3">
-        <f>COUNTIFS(测试集!$D$2:$D$41,A5,测试集!$B$2:$B$41,"前30")</f>
+        <f>COUNTIFS(测试集!$D$2:$D$40,A5,测试集!$B$2:$B$40,"前30")</f>
         <v>9</v>
       </c>
       <c r="C5" s="3">
-        <f>COUNTIFS(测试集!$D$2:$D$41,A5,测试集!$B$2:$B$41,"后10")</f>
+        <f>COUNTIFS(测试集!$D$2:$D$40,A5,测试集!$B$2:$B$40,"后10")</f>
         <v>4</v>
       </c>
       <c r="D5" s="3">
@@ -7774,11 +7780,11 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B6" s="5">
         <f>SUM(B3:B5)</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="5">
         <f>SUM(C3:C5)</f>
@@ -7786,7 +7792,7 @@
       </c>
       <c r="D6" s="5">
         <f>SUM(D3:D5)</f>
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E6" s="5">
         <f>SUM(E3:E5)</f>
@@ -7794,12 +7800,12 @@
       </c>
       <c r="F6" s="3" t="str">
         <f>IF(AND(B6=30,C6=10,D6=E6),"一致","不一致")</f>
-        <v>一致</v>
+        <v>不一致</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1" spans="1:6">
       <c r="A7" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -7809,7 +7815,7 @@
     </row>
     <row r="9" customHeight="1" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -7819,89 +7825,89 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B11" s="7">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"前30")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$L$2:$L$41,"对",测试集!$B$2:$B$41,"前30")/COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$B$2:$B$41,"前30"))</f>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;",测试集!$B$2:$B$40,"前30")=0,"未填",COUNTIFS(测试集!$D$2:$D$40,"违规",测试集!$L$2:$L$40,"对",测试集!$B$2:$B$40,"前30")/COUNTIFS(测试集!$D$2:$D$40,"违规",测试集!$B$2:$B$40,"前30"))</f>
         <v>1</v>
       </c>
       <c r="C11" s="7" t="str">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"后10")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$L$2:$L$41,"对",测试集!$B$2:$B$41,"后10")/COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$B$2:$B$41,"后10"))</f>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;",测试集!$B$2:$B$40,"后10")=0,"未填",COUNTIFS(测试集!$D$2:$D$40,"违规",测试集!$L$2:$L$40,"对",测试集!$B$2:$B$40,"后10")/COUNTIFS(测试集!$D$2:$D$40,"违规",测试集!$B$2:$B$40,"后10"))</f>
         <v>未填</v>
       </c>
       <c r="D11" s="7">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$L$2:$L$41,"对")/COUNTIFS(测试集!$D$2:$D$41,"违规"))</f>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;")=0,"未填",COUNTIFS(测试集!$D$2:$D$40,"违规",测试集!$L$2:$L$40,"对")/COUNTIFS(测试集!$D$2:$D$40,"违规"))</f>
         <v>0.75</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B12" s="7">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"前30")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"合规",测试集!$J$2:$J$41,"违规",测试集!$B$2:$B$41,"前30")/COUNTIFS(测试集!$D$2:$D$41,"合规",测试集!$B$2:$B$41,"前30"))</f>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;",测试集!$B$2:$B$40,"前30")=0,"未填",COUNTIFS(测试集!$D$2:$D$40,"合规",测试集!$J$2:$J$40,"违规",测试集!$B$2:$B$40,"前30")/COUNTIFS(测试集!$D$2:$D$40,"合规",测试集!$B$2:$B$40,"前30"))</f>
         <v>0</v>
       </c>
       <c r="C12" s="7" t="str">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"后10")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"合规",测试集!$J$2:$J$41,"违规",测试集!$B$2:$B$41,"后10")/COUNTIFS(测试集!$D$2:$D$41,"合规",测试集!$B$2:$B$41,"后10"))</f>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;",测试集!$B$2:$B$40,"后10")=0,"未填",COUNTIFS(测试集!$D$2:$D$40,"合规",测试集!$J$2:$J$40,"违规",测试集!$B$2:$B$40,"后10")/COUNTIFS(测试集!$D$2:$D$40,"合规",测试集!$B$2:$B$40,"后10"))</f>
         <v>未填</v>
       </c>
       <c r="D12" s="7">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"合规",测试集!$J$2:$J$41,"违规")/COUNTIFS(测试集!$D$2:$D$41,"合规"))</f>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;")=0,"未填",COUNTIFS(测试集!$D$2:$D$40,"合规",测试集!$J$2:$J$40,"违规")/COUNTIFS(测试集!$D$2:$D$40,"合规"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B13" s="7">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"前30")=0,"未填",COUNTIFS(测试集!$J$2:$J$41,"待复核",测试集!$B$2:$B$41,"前30")/COUNTIFS(测试集!$B$2:$B$41,"前30"))</f>
-        <v>0.166666666666667</v>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;",测试集!$B$2:$B$40,"前30")=0,"未填",COUNTIFS(测试集!$J$2:$J$40,"待复核",测试集!$B$2:$B$40,"前30")/COUNTIFS(测试集!$B$2:$B$40,"前30"))</f>
+        <v>0.172413793103448</v>
       </c>
       <c r="C13" s="7" t="str">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"后10")=0,"未填",COUNTIFS(测试集!$J$2:$J$41,"待复核",测试集!$B$2:$B$41,"后10")/COUNTIFS(测试集!$B$2:$B$41,"后10"))</f>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;",测试集!$B$2:$B$40,"后10")=0,"未填",COUNTIFS(测试集!$J$2:$J$40,"待复核",测试集!$B$2:$B$40,"后10")/COUNTIFS(测试集!$B$2:$B$40,"后10"))</f>
         <v>未填</v>
       </c>
       <c r="D13" s="7">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;")=0,"未填",COUNTIFS(测试集!$J$2:$J$41,"待复核")/COUNTA(测试集!$B$2:$B$41))</f>
-        <v>0.125</v>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;")=0,"未填",COUNTIFS(测试集!$J$2:$J$40,"待复核")/COUNTA(测试集!$B$2:$B$40))</f>
+        <v>0.128205128205128</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B14" s="8">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"前30")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$J$2:$J$41,"待复核",测试集!$B$2:$B$41,"前30"))</f>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;",测试集!$B$2:$B$40,"前30")=0,"未填",COUNTIFS(测试集!$D$2:$D$40,"违规",测试集!$J$2:$J$40,"待复核",测试集!$B$2:$B$40,"前30"))</f>
         <v>0</v>
       </c>
       <c r="C14" s="8" t="str">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;",测试集!$B$2:$B$41,"后10")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$J$2:$J$41,"待复核",测试集!$B$2:$B$41,"后10"))</f>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;",测试集!$B$2:$B$40,"后10")=0,"未填",COUNTIFS(测试集!$D$2:$D$40,"违规",测试集!$J$2:$J$40,"待复核",测试集!$B$2:$B$40,"后10"))</f>
         <v>未填</v>
       </c>
       <c r="D14" s="8">
-        <f>IF(COUNTIFS(测试集!$J$2:$J$41,"&lt;&gt;")=0,"未填",COUNTIFS(测试集!$D$2:$D$41,"违规",测试集!$J$2:$J$41,"待复核"))</f>
+        <f>IF(COUNTIFS(测试集!$J$2:$J$40,"&lt;&gt;")=0,"未填",COUNTIFS(测试集!$D$2:$D$40,"违规",测试集!$J$2:$J$40,"待复核"))</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" ht="99.75" customHeight="1" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -7911,7 +7917,7 @@
     </row>
     <row r="17" customHeight="1" spans="1:6">
       <c r="A17" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -7921,7 +7927,7 @@
     </row>
     <row r="18" ht="120" customHeight="1" spans="1:6">
       <c r="A18" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
